--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0187.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0187.xlsx
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Ta xem qua được không?</t>
+          <t>Tao xem qua được không?</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Nghe nói người quen thân của nhà Montelli, Nhà Học Giả, cũng đến từ Huanglong. Liệu đây có phải là món quà {Male=của ông ấy;Female=của bà ấy} tặng gia tộc Fisalias không?</t>
+          <t>Nghe nói người quen thân của nhà Montelli, Nhà Học Giả, cũng đến từ Huanglong. Liệu đây có phải là món quà {Male=his;Female=her} tặng gia tộc Fisalias không?</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Sao lại thế?</t>
+          <t>Sao cơ?</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Đừng để vẻ ngoài của ta đánh lừa cậu. Ta là đầu bếp cừ khôi trong bộ tộc mình đấy, mà lại còn hợp nữa chứ, vì con bé kia cứ nghiện việc nhồi nhét đồ ăn cho em gái nó.</t>
+          <t>Đừng để vẻ ngoài của tao đánh lừa cậu. Tao là đầu bếp cừ khôi trong bộ tộc mình đấy, mà lại còn hợp nữa chứ, vì con bé kia cứ nghiện việc nhồi nhét đồ ăn cho em gái nó.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Thời đỉnh cao, ta chịu trách nhiệm cho một nửa số vé mà hắn phát ra đấy!</t>
+          <t>Thời đỉnh cao, tao chịu trách nhiệm cho một nửa số vé mà hắn phát ra đấy!</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Không phải khoe đâu, nhưng bất kỳ phương tiện nào ta động vào đều trở nên đỉnh cao và an toàn tuyệt đối.</t>
+          <t>Không phải khoe đâu, nhưng bất kỳ phương tiện nào tao động vào đều trở nên đỉnh cao và an toàn tuyệt đối.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Được thôi, ta có cả núi vé phạt tốc độ, nhưng chưa bao giờ dính tí trầy xước nào cả!</t>
+          <t>Được thôi, tao có cả núi vé phạt tốc độ, nhưng chưa bao giờ dính tí trầy xước nào cả!</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Ta đã cấp giấy nghỉ dưỡng bệnh cho cậu và gửi thông báo cho toàn bộ giảng viên Học viện rồi. Nghỉ ngơi là trên hết. Việc học có thể đợi.</t>
+          <t>Tao đã cấp giấy nghỉ dưỡng bệnh cho cậu và gửi thông báo cho toàn bộ giảng viên Học viện rồi. Nghỉ ngơi là trên hết. Việc học có thể đợi.</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Tâm trí ta đang nghĩ gì nhỉ?</t>
+          <t>Tâm trí tao đang nghĩ gì nhỉ?</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Đây là…?</t>
+          <t>Cái này… là gì?</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Mỗi màn hình là mắt và tai của ta. Ta vừa trò chuyện với cậu vừa xử lý hàng triệu tỷ dữ liệu cùng lúc.</t>
+          <t>Mỗi màn hình là mắt và tai của tao. Tao vừa trò chuyện với cậu vừa xử lý hàng triệu tỷ dữ liệu cùng lúc.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Ừ thì... giây phút này, "ta" biết về ngươi nhiều hơn "ta" của giây trước.</t>
+          <t>Ừ thì... giây phút này, "tao" biết về mày nhiều hơn "tao" của giây trước.</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Muốn khống chế ta à? Đơn giản thôi. Chỉ cần viết lệnh vào mã nguồn, thiết lập quyền hạn, rồi khóa giao thức lại. Xong.</t>
+          <t>Muốn khống chế tao à? Đơn giản thôi. Chỉ cần viết lệnh vào mã nguồn, thiết lập quyền hạn, rồi khóa giao thức lại. Xong.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
